--- a/config/world_boss/union_rank_award.xlsx
+++ b/config/world_boss/union_rank_award.xlsx
@@ -1096,9 +1096,7 @@
           <t>默认值</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1200,7 +1198,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1247,7 +1245,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1294,7 +1292,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1341,7 +1339,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1388,7 +1386,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,7 +1433,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1482,7 +1480,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1502,15 +1500,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" s="1" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1540,7 +1530,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1587,7 +1577,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1634,7 +1624,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1681,7 +1671,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1728,7 +1718,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1775,7 +1765,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1822,7 +1812,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1842,15 +1832,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" s="1" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1880,7 +1862,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1927,7 +1909,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1974,7 +1956,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2021,7 +2003,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2068,7 +2050,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2115,7 +2097,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2162,7 +2144,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2182,15 +2164,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" s="1" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2220,7 +2194,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2267,7 +2241,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2314,7 +2288,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2361,7 +2335,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2408,7 +2382,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2455,7 +2429,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2502,7 +2476,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2522,15 +2496,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" s="1" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2560,7 +2526,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2607,7 +2573,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2654,7 +2620,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2701,7 +2667,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2748,7 +2714,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2795,7 +2761,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2842,7 +2808,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2862,15 +2828,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" s="1" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2900,7 +2858,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2947,7 +2905,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2994,7 +2952,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3041,7 +2999,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3088,7 +3046,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3135,7 +3093,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3182,7 +3140,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3202,15 +3160,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" s="1" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3240,7 +3190,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3287,7 +3237,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3334,7 +3284,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3381,7 +3331,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3428,7 +3378,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3475,7 +3425,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3522,7 +3472,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3542,15 +3492,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" s="1" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3580,7 +3522,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3627,7 +3569,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3674,7 +3616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3721,7 +3663,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3768,7 +3710,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3815,7 +3757,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3862,7 +3804,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3882,15 +3824,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" s="1" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3920,7 +3854,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3967,7 +3901,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4014,7 +3948,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4061,7 +3995,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4108,7 +4042,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4155,7 +4089,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4202,7 +4136,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4222,15 +4156,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" s="1" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4260,7 +4186,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4307,7 +4233,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4354,7 +4280,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4401,7 +4327,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4448,7 +4374,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4495,7 +4421,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4542,7 +4468,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4562,15 +4488,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" s="1" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4600,7 +4518,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4647,7 +4565,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4694,7 +4612,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4741,7 +4659,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4788,7 +4706,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4835,7 +4753,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4882,7 +4800,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4902,15 +4820,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr"/>
       <c r="C91" s="1" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4940,7 +4850,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4987,7 +4897,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5034,7 +4944,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5081,7 +4991,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5128,7 +5038,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5175,7 +5085,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5222,7 +5132,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>世界BOSS獎勵</t>
+          <t>世界BOSS奖励</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
